--- a/nr-doc-core-immunization/ig/StructureDefinition-fr-core-immunization.xlsx
+++ b/nr-doc-core-immunization/ig/StructureDefinition-fr-core-immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T12:14:39+00:00</t>
+    <t>2026-09-17T13:19:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1550,7 +1550,7 @@
     <t>Body site where vaccine was administered.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-immunization-approach-site-code-cisis|20260619134041</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-immunization-approach-site-code-cisis|20260716085851</t>
   </si>
   <si>
     <t>RXR-2</t>
@@ -1571,7 +1571,7 @@
     <t>The path by which the vaccine product is taken into the body.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-immunization-route-code-cisis|20260619134042</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-immunization-route-code-cisis|20260716085852</t>
   </si>
   <si>
     <t>RXR-1</t>
@@ -2090,7 +2090,7 @@
     <t>One possible path to achieve presumed immunity against a disease - within the context of an authority.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ActSubstanceAdministrationImmunizationCode-cisis|20260619134043</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ActSubstanceAdministrationImmunizationCode-cisis|20260716085853</t>
   </si>
   <si>
     <t>Immunization.protocolApplied.authority</t>

--- a/nr-doc-core-immunization/ig/StructureDefinition-fr-core-immunization.xlsx
+++ b/nr-doc-core-immunization/ig/StructureDefinition-fr-core-immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T13:19:58+00:00</t>
+    <t>2026-10-13T08:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1550,7 +1550,7 @@
     <t>Body site where vaccine was administered.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-immunization-approach-site-code-cisis|20260716085851</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-immunization-approach-site-code-cisis|20260916095452</t>
   </si>
   <si>
     <t>RXR-2</t>
@@ -1571,7 +1571,7 @@
     <t>The path by which the vaccine product is taken into the body.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-immunization-route-code-cisis|20260716085852</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-immunization-route-code-cisis|20260916095454</t>
   </si>
   <si>
     <t>RXR-1</t>
@@ -2090,7 +2090,7 @@
     <t>One possible path to achieve presumed immunity against a disease - within the context of an authority.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ActSubstanceAdministrationImmunizationCode-cisis|20260716085853</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ActSubstanceAdministrationImmunizationCode-cisis|20260916095457</t>
   </si>
   <si>
     <t>Immunization.protocolApplied.authority</t>
